--- a/security-configuration-hardening-guide/hcx/4.11/vmware-hcx-security-configuration-guide-411-controls.xlsx
+++ b/security-configuration-hardening-guide/hcx/4.11/vmware-hcx-security-configuration-guide-411-controls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vmware\Projects\Security Configuration Guide\Security Configuration Guide 9\WORKING COPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1002AF13-4DE0-4387-90E6-60E9AC68C53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8534FF6C-1A22-4EB2-AEC6-B958755491DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2004" yWindow="660" windowWidth="57816" windowHeight="20688" xr2:uid="{378E67A8-D089-4FA6-9DFE-D37B9D846B86}"/>
+    <workbookView xWindow="1485" yWindow="525" windowWidth="49725" windowHeight="21120" xr2:uid="{378E67A8-D089-4FA6-9DFE-D37B9D846B86}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="156">
   <si>
     <t>See the included documentation for important guidance and instructions.</t>
   </si>
@@ -237,9 +237,6 @@
     <t>Network Extension Encryption (IPsec)</t>
   </si>
   <si>
-    <t>Disabled for Private Network. Enabled for Public Network.</t>
-  </si>
-  <si>
     <t>Verify that encryption is enabled when creating a Service Mesh. If not Enable encryption.</t>
   </si>
   <si>
@@ -252,15 +249,9 @@
     <t>HCX Service Mesh High Availability (HA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Not Enabled </t>
-  </si>
-  <si>
     <t>Enable the High Availability (HA) option when creating or editing a Service Mesh.</t>
   </si>
   <si>
-    <t>The SSH service on the HCX Manager and Connector appliances is enabled by default for troubleshooting. For a hardened environment, SSH should be disabled if not actively needed, or secured by using key-based authentication and disabling root login.</t>
-  </si>
-  <si>
     <t>SSH Service</t>
   </si>
   <si>
@@ -282,9 +273,6 @@
     <t>hcx-4.network-extension-encryption</t>
   </si>
   <si>
-    <t>Network Extension</t>
-  </si>
-  <si>
     <t>IAC-22, IAC-10, IAC-10.1</t>
   </si>
   <si>
@@ -351,16 +339,7 @@
     <t>This setting specifies the number of consecutive failed login attempts allowed for an HCX appliance (Manager or Connector) user account before the account is locked. This applies to both the admin and root user accounts.</t>
   </si>
   <si>
-    <t>A login banner should be configured for all HCX appliances (Manager and Connector) for both UI and SSH access. This banner should display an appropriate legal notice and warning, stating that the system is for authorized use only.</t>
-  </si>
-  <si>
     <t>HCX Network Extension (L2 stretch) traffic between the source and destination Network Extension (NE) appliances can be encrypted. This setting, configured per Service Mesh, enables Suite-B IPsec encryption for all stretched network traffic.</t>
-  </si>
-  <si>
-    <t>All HCX components (Manager, Connector) and their paired VMware Cloud Foundation components (vCenter, ESX, NSX) must be running versions that are on the official VMware Cloud Foundation Product Interoperability Matrix.</t>
-  </si>
-  <si>
-    <t>HCX appliance updates (for Manager and Connector) are managed via the appliance VAMI (port 9443). Administrators should regularly check for and apply the latest security patches and updates from the official VMware Cloud Foundation repository.</t>
   </si>
   <si>
     <t>Enabling network extension encryption increases CPU usage on the HCX Network Extension appliances.</t>
@@ -524,8 +503,52 @@
     </r>
   </si>
   <si>
+    <t>/etc/security/pwquality.conf</t>
+  </si>
+  <si>
+    <t>VMware HCX Security Configuration Guide</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>Changes to password settings on the appliances may impact connectivity of other solutions, and may negatively impact automated deployment of subordinate HCX components, and will need to be reconfigured after an update or upgrade.</t>
+  </si>
+  <si>
+    <t>fail_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">difok = 8
+minlen = 15
+dcredit = -1
+ucredit = -1
+lcredit = -1
+ocredit = -1
+dictcheck = 1
+enforce_for_root
+</t>
+  </si>
+  <si>
+    <t>The HCX Manager appliance (Cloud and Connector) OS enforces complexity rules for local user accounts (admin, root). These rules should be configured to require a minimum length and a mix of uppercase, lowercase, numbers, and special characters. These settings can be found in /etc/security/pwquality.conf.</t>
+  </si>
+  <si>
+    <t>Various</t>
+  </si>
+  <si>
+    <t>A login banner should be configured for all HCX appliances (Cloud and Connector) for both UI and SSH access. This banner should display an appropriate legal notice and warning, stating that the system is for authorized use only.</t>
+  </si>
+  <si>
+    <t>The SSH service on the Cloud and Connector appliances is enabled by default for troubleshooting. For a hardened environment, SSH should be disabled if not actively needed, or secured by using key-based authentication and disabling root login.</t>
+  </si>
+  <si>
+    <t>All HCX appliances (Cloud and Connector) and all related VMware Cloud Foundation components must have their clocks synchronized to a reliable, central Network Time Protocol (NTP) server. Since HCX automatically deploys other component VMs from the HCX Manager, this setting must be configured on the HCX Manager prior to deployment.</t>
+  </si>
+  <si>
+    <t>All HCX components (Cloud, Connector) and their paired VMware Cloud Foundation components (vCenter, ESX, NSX) must be running versions that are on the official VMware Cloud Foundation Product Interoperability Matrix.</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">This setting defines the period, in seconds, that an HCX appliance (Manager and Connector) user account remains locked after the maximum number of failed login attempts is exceeded. This applies to the admin and root user accounts for the appliance's OS and VAMI. Use following command&gt; </t>
+      <t xml:space="preserve">This setting defines the period, in seconds, that an HCX appliance (Cloud and Connector) user account remains locked after the maximum number of failed login attempts is exceeded. This applies to the admin and root user accounts for the appliance's OS and VAMI. Use following command&gt; </t>
     </r>
     <r>
       <rPr>
@@ -540,57 +563,211 @@
     </r>
   </si>
   <si>
-    <t>/etc/security/pwquality.conf</t>
-  </si>
-  <si>
-    <t>VMware HCX Security Configuration Guide</t>
-  </si>
-  <si>
-    <t>Advanced</t>
-  </si>
-  <si>
-    <t>Changes to password settings on the appliances may impact connectivity of other solutions, and may negatively impact automated deployment of subordinate HCX components, and will need to be reconfigured after an update or upgrade.</t>
-  </si>
-  <si>
-    <t>Version 411-20251201-01</t>
-  </si>
-  <si>
-    <t>HCX Manager</t>
-  </si>
-  <si>
-    <t>fail_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">difok = 8
-minlen = 15
-dcredit = -1
-ucredit = -1
-lcredit = -1
-ocredit = -1
-dictcheck = 1
-enforce_for_root
-</t>
-  </si>
-  <si>
-    <t>The HCX Manager appliance (Cloud and Connector) OS enforces complexity rules for local user accounts (admin, root). These rules should be configured to require a minimum length and a mix of uppercase, lowercase, numbers, and special characters. These settings can be found in /etc/security/pwquality.conf.</t>
-  </si>
-  <si>
-    <t>Various</t>
-  </si>
-  <si>
-    <t>All HCX appliances (Manager, Connector, and Service Mesh appliances) should be configured to forward their logs to a central, remote syslog server (e.g., VCF Operations for Logs or another SIEM solution). This ensures logs are preserved and aggregated for analysis. This is configured in the VAMI of the HCX Manager/Connector. Since HCX automatically deploys other component VMs from the HCX Manager, this setting must be configured on the HCX Manager prior to deployment.</t>
-  </si>
-  <si>
-    <t>All HCX appliances (Manager and Connector) and all related VMware Cloud Foundation components must have their clocks synchronized to a reliable, central Network Time Protocol (NTP) server. Since HCX automatically deploys other component VMs from the HCX Manager, this setting must be configured on the HCX Manager prior to deployment.</t>
+    <t>HCX appliance updates (for Cloud and Connector) are managed via the appliance VAMI (port 9443). Administrators should regularly check for and apply the latest security patches and updates from the official VMware Cloud Foundation repository.</t>
+  </si>
+  <si>
+    <t>Disabled</t>
+  </si>
+  <si>
+    <t>REST API Assessment</t>
+  </si>
+  <si>
+    <t>REST API Remediation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All HCX appliances (Cloud, Connector, NE, and IX appliances) should be configured to forward their logs to a central, remote syslog server (e.g., VCF Operations for Logs or another SIEM solution). This ensures logs are preserved and aggregated for analysis. This is configured in the VAMI of the HCX Manager/Connector. Since HCX automatically deploys other component VMs from the HCX Manager, this setting must be configured on the HCX Manager prior to deployment. If these settings are modified after the service mesh is created a "force sync" is required. Force Sync can also be performed via APIs. </t>
+  </si>
+  <si>
+    <t>1. Configure syslog server API: 
+PUT https://&lt;hcx-manager-ip&gt;:9443/system/syslogserver
+Request:
+{
+"syslogServer": "string",
+"port": "int",
+"protocol": "string",
+"secondarySyslogServer": "string",
+"secondaryPort": "int",
+"secondaryProtocol": "string"
+}
+Response:
+Success:
+{
+  "syslogServer": "string",
+  "port": "string",
+  "protocol": "string",
+  "secondarySyslogServer": "string",
+  "secondaryPort": "string",
+  "secondaryProtocol": "string"
+}
+Failure:
+{
+  "errorCode": "integer",
+  "errorMessage": "string"
+} 
+2. Force sync DP appliance API:
+POST https://&lt;hcx-manager-ip&gt;/hybridity/api/interconnect/appliances/&lt;appliance-id&gt;/forceSync?local=&lt;boolean&gt;&amp;force=&lt;boolean&gt;
+Response:
+{
+  "data": {
+    "interconnectTaskId": "string",
+    "applianceId": "string"
+  },
+  "warnings": [
+    {
+      "code": "string",
+      "message": "string"
+    }
+  ],
+  "errors": [
+    {
+      "code": "string",
+      "message": "string"
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>1. Enable HA API:
+POST https://&lt;hcx-manager-ip&gt;/hybridity/api/interconnect/appliances/ha/groups
+Request:
+{
+  "appliances": ["string"],
+  "policyInfo": {
+    "policy": "string"
+  },
+  "groupId": "string"
+}
+Response:
+{
+  "data": {
+    "interconnectTaskId": "string",
+    "groupId": "string"
+  },
+  "warnings": [
+    {
+      "code": "string",
+      "message": "string"
+    }
+  ],
+  "errors": [
+    {
+      "code": "string",
+      "message": "string"
+    }
+  ]
+}
+2. Check HA status API:
+GET https://&lt;hcx-manager-ip&gt;/hybridity/api/interconnect/appliances/ha/groups/{groupId}
+Response:
+{
+  "groupId": "string",
+  "name": "string",
+  "serviceMeshId": "string",
+  "groupType": "string",
+  "groupMembers": [
+    {
+      "applianceId": "string",
+      "applianceName": "string",
+      "peerApplianceId": "string",
+      "peerApplianceName": "string",
+      "role": "string",
+      "clusterId": "string",
+      "peerClusterId": "string",
+      "location": "string"
+    }
+  ],
+  "policyInfo": {
+    "policy": "string"
+  },
+  "status": {
+    "groupState": "string",
+    "statusMessage": "string",
+    "availabilityState": "string",
+    "availabilityDescription": "string"
+  }
+}</t>
+  </si>
+  <si>
+    <t>https://{hcx-manager}:9443/components/ssh/status</t>
+  </si>
+  <si>
+    <t>POST: https://{hcx-manager}:9443/components/ssh?action=start</t>
+  </si>
+  <si>
+    <t>https://{hcx-manager}/hybridity/api/endpointInfo</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>https://{hcx-manager}:9443/system/timesettings</t>
+  </si>
+  <si>
+    <t>PUT: https://{hcx-manager}:9443/system/timesettings
+Request:
+{
+  "ntpServer": [
+    "192.19.189.10",
+    "192.19.189.10"
+  ],
+  "datetime": "12/02/2025 06:46:17",
+  "timezone": "UTC"
+}</t>
+  </si>
+  <si>
+    <t>GET: https://{hcx-manager}/hybridity/api/endpointInfo</t>
+  </si>
+  <si>
+    <t>Control Type</t>
+  </si>
+  <si>
+    <t>Technical</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Base via HCX Manager</t>
+  </si>
+  <si>
+    <t>Version 411-20260224-01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -655,13 +832,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
@@ -675,6 +845,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -725,52 +901,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="25">
     <dxf>
       <font>
         <strike val="0"/>
@@ -790,21 +982,30 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -826,7 +1027,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -839,8 +1040,72 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -862,7 +1127,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -875,8 +1140,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -898,7 +1161,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -911,8 +1174,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -934,7 +1195,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -947,8 +1208,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -970,7 +1229,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -983,8 +1242,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1006,7 +1263,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1019,8 +1276,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1042,7 +1297,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1055,8 +1310,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1078,7 +1331,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1091,8 +1344,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1114,7 +1365,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1127,8 +1378,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1150,7 +1399,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1163,8 +1412,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1186,7 +1433,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1199,8 +1446,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1222,7 +1467,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1235,8 +1480,39 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1258,7 +1534,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1271,8 +1547,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1294,7 +1568,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1307,8 +1581,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1330,7 +1602,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1343,8 +1615,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1366,7 +1636,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1379,8 +1649,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1402,7 +1670,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1415,8 +1683,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1438,7 +1704,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1451,8 +1717,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1474,37 +1738,26 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1526,31 +1779,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3695A651-C5D3-475E-B0F1-62D95BE20D6E}" name="Table1" displayName="Table1" ref="A1:S16" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20">
-  <autoFilter ref="A1:S16" xr:uid="{3695A651-C5D3-475E-B0F1-62D95BE20D6E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S16">
-    <sortCondition ref="A2:A16"/>
-  </sortState>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{79C2AF0A-5390-4E9C-B0D5-8710D43BFCA8}" name="SCG ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{3A2F9A8A-E9C4-43A8-8594-3E2B9A6D5730}" name="Secure Controls_x000a_Framework ID" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{04C83ECD-7936-4E48-94C3-11B7501981A9}" name="DISA STIG ID" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{0C22C20C-5D4F-427F-9F5F-9E803CF25C95}" name="PCI DSS 4.0.1 ID" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{A908CAC9-5614-48A4-97C3-70CA9AC8DAFE}" name="Component_x000a_Name" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{E16C3EB7-CA62-41B0-81A3-43D994DC67B8}" name="Component Version" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{895DEAD4-BA35-4DEB-8BDB-962B3C89AD91}" name="Feature/Function" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{71DF3195-B3BB-4383-997D-CEDC42E35F5E}" name="Description/Title" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{426E1751-524C-44E0-BDFE-1D437FA86969}" name="Discussion" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{FE8DA64B-D7B6-4390-92F8-5979922A1CF8}" name="Potential Functional Impact if Default Value is Changed" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{B910FBF8-6292-4A9B-B845-87CB8C60FA3E}" name="Implementation_x000a_Priority" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{9BFF0C05-282D-4957-8499-73407BD57496}" name="Configuration Parameter" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{7AAC1EEF-6538-49BC-B64E-854CF38BD12C}" name="Installation Default Value" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{CD721173-154F-4E21-BC3D-DB2AC5F8A19C}" name="Baseline Suggested Value" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{AA97B976-1568-486E-88B7-7A4EA28C60EB}" name="Is the Default?" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{02A4FA27-33A4-43FE-84CE-5CD5C84AAA7A}" name="Action Needed" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{10B1F9B6-A49A-438E-AC43-8517B9CD2D77}" name="Setting Location" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{936E61C0-BF2D-4333-81AE-CF1CFBD1551E}" name="PowerCLI Command Assessment" dataDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{5409B494-3A6E-419E-93EC-5CDA59C980DB}" name="PowerCLI Command Remediation" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3695A651-C5D3-475E-B0F1-62D95BE20D6E}" name="Table1" displayName="Table1" ref="A1:V16" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="24">
+  <autoFilter ref="A1:V16" xr:uid="{3695A651-C5D3-475E-B0F1-62D95BE20D6E}"/>
+  <tableColumns count="22">
+    <tableColumn id="1" xr3:uid="{79C2AF0A-5390-4E9C-B0D5-8710D43BFCA8}" name="SCG ID" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{3A2F9A8A-E9C4-43A8-8594-3E2B9A6D5730}" name="Secure Controls_x000a_Framework ID" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{04C83ECD-7936-4E48-94C3-11B7501981A9}" name="DISA STIG ID" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{0C22C20C-5D4F-427F-9F5F-9E803CF25C95}" name="PCI DSS 4.0.1 ID" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{A908CAC9-5614-48A4-97C3-70CA9AC8DAFE}" name="Component_x000a_Name" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{E16C3EB7-CA62-41B0-81A3-43D994DC67B8}" name="Component Version" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{895DEAD4-BA35-4DEB-8BDB-962B3C89AD91}" name="Feature/Function" dataDxfId="17"/>
+    <tableColumn id="22" xr3:uid="{D5C7BF26-1D11-4267-B152-F653B2A06DA0}" name="Control Type" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{71DF3195-B3BB-4383-997D-CEDC42E35F5E}" name="Description/Title" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{426E1751-524C-44E0-BDFE-1D437FA86969}" name="Discussion" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{FE8DA64B-D7B6-4390-92F8-5979922A1CF8}" name="Potential Functional Impact if Default Value is Changed" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{B910FBF8-6292-4A9B-B845-87CB8C60FA3E}" name="Implementation_x000a_Priority" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{9BFF0C05-282D-4957-8499-73407BD57496}" name="Configuration Parameter" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{7AAC1EEF-6538-49BC-B64E-854CF38BD12C}" name="Installation Default Value" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{CD721173-154F-4E21-BC3D-DB2AC5F8A19C}" name="Baseline Suggested Value" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{AA97B976-1568-486E-88B7-7A4EA28C60EB}" name="Is the Default?" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{02A4FA27-33A4-43FE-84CE-5CD5C84AAA7A}" name="Action Needed" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{10B1F9B6-A49A-438E-AC43-8517B9CD2D77}" name="Setting Location" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{936E61C0-BF2D-4333-81AE-CF1CFBD1551E}" name="PowerCLI Command Assessment" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{63B187A1-3960-461E-B0B9-65EAC6B513D2}" name="PowerCLI Command Remediation" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{99812249-2B93-4E22-B188-372FD60D0537}" name="REST API Assessment" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{5409B494-3A6E-419E-93EC-5CDA59C980DB}" name="REST API Remediation" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1874,54 +2127,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D633219-EF3A-40A9-A077-828D0951CCAB}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="161.109375" customWidth="1"/>
+    <col min="1" max="1" width="161.140625" style="18" customWidth="1"/>
+    <col min="2" max="16384" width="8.85546875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>133</v>
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>136</v>
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" ht="105" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:1" ht="294" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" ht="294" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
   </sheetData>
@@ -1931,976 +2185,1121 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBA3DAB-E918-4651-919A-86FFFAAB5500}">
-  <dimension ref="A1:S16"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V16"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="71.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" style="5" customWidth="1"/>
-    <col min="3" max="4" width="26.44140625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="93.109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="104.88671875" style="6" customWidth="1"/>
-    <col min="10" max="10" width="70.6640625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="23.44140625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="82.109375" style="6" customWidth="1"/>
-    <col min="13" max="13" width="30.44140625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="47.44140625" style="6" customWidth="1"/>
-    <col min="15" max="15" width="16.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="39.109375" style="6" customWidth="1"/>
-    <col min="18" max="18" width="144.6640625" style="6" customWidth="1"/>
-    <col min="19" max="19" width="143.109375" style="6" customWidth="1"/>
-    <col min="20" max="16384" width="9.109375" style="6"/>
+    <col min="1" max="1" width="32.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="5" customWidth="1"/>
+    <col min="3" max="4" width="26.42578125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" style="5" customWidth="1"/>
+    <col min="9" max="9" width="93.140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="104.85546875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="70.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="82.140625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="30.42578125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="47.42578125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.140625" style="5" customWidth="1"/>
+    <col min="19" max="21" width="144.7109375" style="5" customWidth="1"/>
+    <col min="22" max="22" width="143.140625" style="5" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="7" t="s">
         <v>21</v>
       </c>
+      <c r="U1" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" ht="78" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="V6" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U7" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="V7" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U8" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="V8" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="11" t="s">
+      <c r="C9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N11" s="9">
+        <v>3</v>
+      </c>
+      <c r="O11" s="9">
+        <v>3</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="V11" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="N12" s="9">
+        <v>900</v>
+      </c>
+      <c r="O12" s="8">
+        <v>900</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V12" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="N14" s="9">
+        <v>5</v>
+      </c>
+      <c r="O14" s="9">
+        <v>10</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="N15" s="9">
+        <v>99999</v>
+      </c>
+      <c r="O15" s="9">
+        <v>99999</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V15" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="J2" s="11" t="s">
+      <c r="K16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="11" t="s">
+      <c r="M16" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="P16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q6" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="R6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S6" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="R7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="O8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="R8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="R9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S9" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="M10" s="10">
-        <v>86400</v>
-      </c>
-      <c r="N10" s="10">
-        <v>0</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="R10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S10" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="M11" s="11">
-        <v>3</v>
-      </c>
-      <c r="N11" s="11">
-        <v>3</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q11" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="R11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S11" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="M12" s="11">
-        <v>900</v>
-      </c>
-      <c r="N12" s="10">
-        <v>900</v>
-      </c>
-      <c r="O12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="P12" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q12" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="R12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="S12" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="140.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q13" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="R13" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="S13" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="M14" s="11">
-        <v>10</v>
-      </c>
-      <c r="N14" s="11">
-        <v>10</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q14" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="R14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="S14" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="M15" s="11">
-        <v>99999</v>
-      </c>
-      <c r="N15" s="11">
-        <v>99999</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="R15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="S15" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="O16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="P16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="R16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="S16" s="11" t="s">
-        <v>24</v>
+      <c r="S16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U16" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="V16" s="13" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:S16">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:V16">
     <sortCondition ref="A1:A16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/security-configuration-hardening-guide/hcx/4.11/vmware-hcx-security-configuration-guide-411-controls.xlsx
+++ b/security-configuration-hardening-guide/hcx/4.11/vmware-hcx-security-configuration-guide-411-controls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vmware\Projects\Security Configuration Guide\Security Configuration Guide 9\WORKING COPY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vcf-security-and-compliance-guidelines\security-configuration-hardening-guide\hcx\4.11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8534FF6C-1A22-4EB2-AEC6-B958755491DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E33B40-B4B6-4820-8380-652862006FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="525" windowWidth="49725" windowHeight="21120" xr2:uid="{378E67A8-D089-4FA6-9DFE-D37B9D846B86}"/>
+    <workbookView xWindow="2004" yWindow="1548" windowWidth="56784" windowHeight="23520" xr2:uid="{378E67A8-D089-4FA6-9DFE-D37B9D846B86}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="145">
   <si>
     <t>See the included documentation for important guidance and instructions.</t>
   </si>
@@ -569,153 +569,7 @@
     <t>Disabled</t>
   </si>
   <si>
-    <t>REST API Assessment</t>
-  </si>
-  <si>
-    <t>REST API Remediation</t>
-  </si>
-  <si>
     <t xml:space="preserve">All HCX appliances (Cloud, Connector, NE, and IX appliances) should be configured to forward their logs to a central, remote syslog server (e.g., VCF Operations for Logs or another SIEM solution). This ensures logs are preserved and aggregated for analysis. This is configured in the VAMI of the HCX Manager/Connector. Since HCX automatically deploys other component VMs from the HCX Manager, this setting must be configured on the HCX Manager prior to deployment. If these settings are modified after the service mesh is created a "force sync" is required. Force Sync can also be performed via APIs. </t>
-  </si>
-  <si>
-    <t>1. Configure syslog server API: 
-PUT https://&lt;hcx-manager-ip&gt;:9443/system/syslogserver
-Request:
-{
-"syslogServer": "string",
-"port": "int",
-"protocol": "string",
-"secondarySyslogServer": "string",
-"secondaryPort": "int",
-"secondaryProtocol": "string"
-}
-Response:
-Success:
-{
-  "syslogServer": "string",
-  "port": "string",
-  "protocol": "string",
-  "secondarySyslogServer": "string",
-  "secondaryPort": "string",
-  "secondaryProtocol": "string"
-}
-Failure:
-{
-  "errorCode": "integer",
-  "errorMessage": "string"
-} 
-2. Force sync DP appliance API:
-POST https://&lt;hcx-manager-ip&gt;/hybridity/api/interconnect/appliances/&lt;appliance-id&gt;/forceSync?local=&lt;boolean&gt;&amp;force=&lt;boolean&gt;
-Response:
-{
-  "data": {
-    "interconnectTaskId": "string",
-    "applianceId": "string"
-  },
-  "warnings": [
-    {
-      "code": "string",
-      "message": "string"
-    }
-  ],
-  "errors": [
-    {
-      "code": "string",
-      "message": "string"
-    }
-  ]
-}</t>
-  </si>
-  <si>
-    <t>1. Enable HA API:
-POST https://&lt;hcx-manager-ip&gt;/hybridity/api/interconnect/appliances/ha/groups
-Request:
-{
-  "appliances": ["string"],
-  "policyInfo": {
-    "policy": "string"
-  },
-  "groupId": "string"
-}
-Response:
-{
-  "data": {
-    "interconnectTaskId": "string",
-    "groupId": "string"
-  },
-  "warnings": [
-    {
-      "code": "string",
-      "message": "string"
-    }
-  ],
-  "errors": [
-    {
-      "code": "string",
-      "message": "string"
-    }
-  ]
-}
-2. Check HA status API:
-GET https://&lt;hcx-manager-ip&gt;/hybridity/api/interconnect/appliances/ha/groups/{groupId}
-Response:
-{
-  "groupId": "string",
-  "name": "string",
-  "serviceMeshId": "string",
-  "groupType": "string",
-  "groupMembers": [
-    {
-      "applianceId": "string",
-      "applianceName": "string",
-      "peerApplianceId": "string",
-      "peerApplianceName": "string",
-      "role": "string",
-      "clusterId": "string",
-      "peerClusterId": "string",
-      "location": "string"
-    }
-  ],
-  "policyInfo": {
-    "policy": "string"
-  },
-  "status": {
-    "groupState": "string",
-    "statusMessage": "string",
-    "availabilityState": "string",
-    "availabilityDescription": "string"
-  }
-}</t>
-  </si>
-  <si>
-    <t>https://{hcx-manager}:9443/components/ssh/status</t>
-  </si>
-  <si>
-    <t>POST: https://{hcx-manager}:9443/components/ssh?action=start</t>
-  </si>
-  <si>
-    <t>https://{hcx-manager}/hybridity/api/endpointInfo</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>https://{hcx-manager}:9443/system/timesettings</t>
-  </si>
-  <si>
-    <t>PUT: https://{hcx-manager}:9443/system/timesettings
-Request:
-{
-  "ntpServer": [
-    "192.19.189.10",
-    "192.19.189.10"
-  ],
-  "datetime": "12/02/2025 06:46:17",
-  "timezone": "UTC"
-}</t>
-  </si>
-  <si>
-    <t>GET: https://{hcx-manager}/hybridity/api/endpointInfo</t>
   </si>
   <si>
     <t>Control Type</t>
@@ -737,7 +591,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,12 +700,6 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -901,7 +749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -939,9 +787,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -954,7 +799,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -962,119 +806,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <font>
         <b val="0"/>
@@ -1754,10 +1486,55 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1779,31 +1556,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3695A651-C5D3-475E-B0F1-62D95BE20D6E}" name="Table1" displayName="Table1" ref="A1:V16" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="24">
-  <autoFilter ref="A1:V16" xr:uid="{3695A651-C5D3-475E-B0F1-62D95BE20D6E}"/>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{79C2AF0A-5390-4E9C-B0D5-8710D43BFCA8}" name="SCG ID" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{3A2F9A8A-E9C4-43A8-8594-3E2B9A6D5730}" name="Secure Controls_x000a_Framework ID" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{04C83ECD-7936-4E48-94C3-11B7501981A9}" name="DISA STIG ID" dataDxfId="21"/>
-    <tableColumn id="19" xr3:uid="{0C22C20C-5D4F-427F-9F5F-9E803CF25C95}" name="PCI DSS 4.0.1 ID" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{A908CAC9-5614-48A4-97C3-70CA9AC8DAFE}" name="Component_x000a_Name" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{E16C3EB7-CA62-41B0-81A3-43D994DC67B8}" name="Component Version" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{895DEAD4-BA35-4DEB-8BDB-962B3C89AD91}" name="Feature/Function" dataDxfId="17"/>
-    <tableColumn id="22" xr3:uid="{D5C7BF26-1D11-4267-B152-F653B2A06DA0}" name="Control Type" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{71DF3195-B3BB-4383-997D-CEDC42E35F5E}" name="Description/Title" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{426E1751-524C-44E0-BDFE-1D437FA86969}" name="Discussion" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{FE8DA64B-D7B6-4390-92F8-5979922A1CF8}" name="Potential Functional Impact if Default Value is Changed" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{B910FBF8-6292-4A9B-B845-87CB8C60FA3E}" name="Implementation_x000a_Priority" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{9BFF0C05-282D-4957-8499-73407BD57496}" name="Configuration Parameter" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{7AAC1EEF-6538-49BC-B64E-854CF38BD12C}" name="Installation Default Value" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{CD721173-154F-4E21-BC3D-DB2AC5F8A19C}" name="Baseline Suggested Value" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{AA97B976-1568-486E-88B7-7A4EA28C60EB}" name="Is the Default?" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{02A4FA27-33A4-43FE-84CE-5CD5C84AAA7A}" name="Action Needed" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{10B1F9B6-A49A-438E-AC43-8517B9CD2D77}" name="Setting Location" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{936E61C0-BF2D-4333-81AE-CF1CFBD1551E}" name="PowerCLI Command Assessment" dataDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{63B187A1-3960-461E-B0B9-65EAC6B513D2}" name="PowerCLI Command Remediation" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{99812249-2B93-4E22-B188-372FD60D0537}" name="REST API Assessment" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{5409B494-3A6E-419E-93EC-5CDA59C980DB}" name="REST API Remediation" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3695A651-C5D3-475E-B0F1-62D95BE20D6E}" name="Table1" displayName="Table1" ref="A1:T16" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21">
+  <autoFilter ref="A1:T16" xr:uid="{3695A651-C5D3-475E-B0F1-62D95BE20D6E}"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{79C2AF0A-5390-4E9C-B0D5-8710D43BFCA8}" name="SCG ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{3A2F9A8A-E9C4-43A8-8594-3E2B9A6D5730}" name="Secure Controls_x000a_Framework ID" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{04C83ECD-7936-4E48-94C3-11B7501981A9}" name="DISA STIG ID" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{0C22C20C-5D4F-427F-9F5F-9E803CF25C95}" name="PCI DSS 4.0.1 ID" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{A908CAC9-5614-48A4-97C3-70CA9AC8DAFE}" name="Component_x000a_Name" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{E16C3EB7-CA62-41B0-81A3-43D994DC67B8}" name="Component Version" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{895DEAD4-BA35-4DEB-8BDB-962B3C89AD91}" name="Feature/Function" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{D5C7BF26-1D11-4267-B152-F653B2A06DA0}" name="Control Type" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{71DF3195-B3BB-4383-997D-CEDC42E35F5E}" name="Description/Title" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{426E1751-524C-44E0-BDFE-1D437FA86969}" name="Discussion" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{FE8DA64B-D7B6-4390-92F8-5979922A1CF8}" name="Potential Functional Impact if Default Value is Changed" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{B910FBF8-6292-4A9B-B845-87CB8C60FA3E}" name="Implementation_x000a_Priority" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{9BFF0C05-282D-4957-8499-73407BD57496}" name="Configuration Parameter" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{7AAC1EEF-6538-49BC-B64E-854CF38BD12C}" name="Installation Default Value" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{CD721173-154F-4E21-BC3D-DB2AC5F8A19C}" name="Baseline Suggested Value" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{AA97B976-1568-486E-88B7-7A4EA28C60EB}" name="Is the Default?" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{02A4FA27-33A4-43FE-84CE-5CD5C84AAA7A}" name="Action Needed" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{10B1F9B6-A49A-438E-AC43-8517B9CD2D77}" name="Setting Location" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{936E61C0-BF2D-4333-81AE-CF1CFBD1551E}" name="PowerCLI Command Assessment" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{63B187A1-3960-461E-B0B9-65EAC6B513D2}" name="PowerCLI Command Remediation" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2127,55 +1902,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D633219-EF3A-40A9-A077-828D0951CCAB}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="161.140625" style="18" customWidth="1"/>
-    <col min="2" max="16384" width="8.85546875" style="18"/>
+    <col min="1" max="1" width="161.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>155</v>
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="21" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="105" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:1" ht="294" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="294" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="21" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
   </sheetData>
@@ -2185,32 +1959,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBA3DAB-E918-4651-919A-86FFFAAB5500}">
-  <dimension ref="A1:V16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T16"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="5" customWidth="1"/>
-    <col min="3" max="4" width="26.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="5" customWidth="1"/>
+    <col min="3" max="4" width="26.44140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" style="5" customWidth="1"/>
-    <col min="9" max="9" width="93.140625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="104.85546875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="70.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="82.140625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="30.42578125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="47.42578125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="39.140625" style="5" customWidth="1"/>
-    <col min="19" max="21" width="144.7109375" style="5" customWidth="1"/>
-    <col min="22" max="22" width="143.140625" style="5" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="5"/>
+    <col min="9" max="9" width="93.109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="104.88671875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="70.6640625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="82.109375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="30.44140625" style="5" customWidth="1"/>
+    <col min="15" max="15" width="47.44140625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="16.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.109375" style="5" customWidth="1"/>
+    <col min="19" max="20" width="144.6640625" style="5" customWidth="1"/>
+    <col min="21" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
@@ -2233,7 +2006,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>10</v>
@@ -2271,14 +2044,8 @@
       <c r="T1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="V1" s="12" t="s">
-        <v>140</v>
-      </c>
     </row>
-    <row r="2" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>50</v>
       </c>
@@ -2298,16 +2065,16 @@
         <v>57</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>84</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>22</v>
@@ -2339,14 +2106,8 @@
       <c r="T2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="V2" s="13" t="s">
-        <v>142</v>
-      </c>
     </row>
-    <row r="3" spans="1:22" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>51</v>
       </c>
@@ -2366,10 +2127,10 @@
         <v>57</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>85</v>
@@ -2407,14 +2168,8 @@
       <c r="T3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="V3" s="9" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="4" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>99</v>
       </c>
@@ -2437,7 +2192,7 @@
         <v>102</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>100</v>
@@ -2475,14 +2230,8 @@
       <c r="T4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="5" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>73</v>
       </c>
@@ -2505,7 +2254,7 @@
         <v>103</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>86</v>
@@ -2528,7 +2277,7 @@
       <c r="O5" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="P5" s="14" t="s">
+      <c r="P5" s="13" t="s">
         <v>28</v>
       </c>
       <c r="Q5" s="8" t="s">
@@ -2543,14 +2292,8 @@
       <c r="T5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="V5" s="9" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="6" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>98</v>
       </c>
@@ -2573,7 +2316,7 @@
         <v>103</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>90</v>
@@ -2611,14 +2354,8 @@
       <c r="T6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U6" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="V6" s="13" t="s">
-        <v>143</v>
-      </c>
     </row>
-    <row r="7" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>52</v>
       </c>
@@ -2638,10 +2375,10 @@
         <v>57</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>91</v>
@@ -2658,16 +2395,16 @@
       <c r="M7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="15" t="s">
         <v>138</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="P7" s="17" t="s">
+      <c r="P7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="Q7" s="16" t="s">
+      <c r="Q7" s="15" t="s">
         <v>29</v>
       </c>
       <c r="R7" s="9" t="s">
@@ -2679,14 +2416,8 @@
       <c r="T7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U7" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="V7" s="13" t="s">
-        <v>145</v>
-      </c>
     </row>
-    <row r="8" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>53</v>
       </c>
@@ -2706,10 +2437,10 @@
         <v>57</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>92</v>
@@ -2747,14 +2478,8 @@
       <c r="T8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U8" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="V8" s="13" t="s">
-        <v>147</v>
-      </c>
     </row>
-    <row r="9" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>54</v>
       </c>
@@ -2774,10 +2499,10 @@
         <v>57</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>93</v>
@@ -2815,14 +2540,8 @@
       <c r="T9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="V9" s="13" t="s">
-        <v>149</v>
-      </c>
     </row>
-    <row r="10" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>109</v>
       </c>
@@ -2842,10 +2561,10 @@
         <v>57</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>81</v>
@@ -2883,14 +2602,8 @@
       <c r="T10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="V10" s="9" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="11" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>110</v>
       </c>
@@ -2910,10 +2623,10 @@
         <v>57</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>82</v>
@@ -2951,14 +2664,8 @@
       <c r="T11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="V11" s="9" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="12" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>111</v>
       </c>
@@ -2978,10 +2685,10 @@
         <v>57</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>83</v>
@@ -3019,14 +2726,8 @@
       <c r="T12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="U12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="V12" s="8" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="13" spans="1:22" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>106</v>
       </c>
@@ -3046,10 +2747,10 @@
         <v>57</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>87</v>
@@ -3087,14 +2788,8 @@
       <c r="T13" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="U13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="V13" s="8" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="14" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>107</v>
       </c>
@@ -3114,10 +2809,10 @@
         <v>57</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>88</v>
@@ -3155,14 +2850,8 @@
       <c r="T14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="U14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="V14" s="8" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="15" spans="1:22" ht="63" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>108</v>
       </c>
@@ -3182,10 +2871,10 @@
         <v>57</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>89</v>
@@ -3223,14 +2912,8 @@
       <c r="T15" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="U15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="V15" s="8" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="16" spans="1:22" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>55</v>
       </c>
@@ -3250,10 +2933,10 @@
         <v>57</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>94</v>
@@ -3279,7 +2962,7 @@
       <c r="P16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="Q16" s="15" t="s">
+      <c r="Q16" s="14" t="s">
         <v>29</v>
       </c>
       <c r="R16" s="9" t="s">
@@ -3291,15 +2974,9 @@
       <c r="T16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U16" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="V16" s="13" t="s">
-        <v>147</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:V16">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:T16">
     <sortCondition ref="A1:A16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
